--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text_1sthalf/lang_multi_text_1sthalf__lore__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text_1sthalf/lang_multi_text_1sthalf__lore__part_0001.xlsx
@@ -1561,7 +1561,7 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>Sau khi đánh bại Denia, cậu chuẩn bị vượt qua Stridergate. Hiyuki do dự trước khi cậu ra đi, tự hỏi liệu một vị cứu tinh có nên đi trên con đường cô độc. Dẫn dắt người khác theo con đường này, theo cô, chỉ mang lại bất hạnh—như đã từng xảy ra với Aemeath. Nhưng cậu nói với cô rằng cậu không hề hối tiếc, và luôn tự hào về con người Aemeath. Chính nhờ cô ấy, cậu không còn cảm thấy cô đơn trên con đường này.
-Lời nói của cậu khiến Hiyuki nhớ đến chị gái mình, Gyokuro. Một sự thay đổi thoáng qua trên Dodget mặt cô, rồi cô thú nhận rằng mình hơi "ghen tị" với cậu, trước khi nói sẽ đợi cậu trở về an toàn ở đây.</t>
+Lời nói của cậu khiến Hiyuki nhớ đến chị gái mình, Gyokuro. Một sự thay đổi thoáng qua trên nét mặt cô, rồi cô thú nhận rằng mình hơi "ghen tị" với cậu, trước khi nói sẽ đợi cậu trở về an toàn ở đây.</t>
         </is>
       </c>
     </row>
